--- a/sample-data/dummy_participants.xlsx
+++ b/sample-data/dummy_participants.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\PycharmProjects\certificate lib\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf04e0e5136f1fdf/Desktop/projects/certi-lib/sample-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9DF29E-EB33-4CDE-8566-2999E4FAC48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{2A9DF29E-EB33-4CDE-8566-2999E4FAC48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{293CF45A-5223-4D6B-8655-0C603D7228CF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Participants" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>name</t>
   </si>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t>om.agarwal16805@gmail.com</t>
+  </si>
+  <si>
+    <t>Sahil Vevariya</t>
+  </si>
+  <si>
+    <t>sahil.vevariya10948@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -467,15 +473,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -497,7 +503,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -508,7 +514,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -519,7 +525,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -530,7 +536,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -541,7 +547,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -550,11 +556,23 @@
       </c>
       <c r="C7">
         <v>590016363</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>590016364</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{792C36EB-40D7-4D43-9FF9-68715D7F27E7}"/>
+    <hyperlink ref="B8" r:id="rId2" xr:uid="{AA96C7BA-D153-4F25-B0EB-8C5885B69EAA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
